--- a/ig/DM-SIDOBA/ValueSet-jdv-j407-type-repas-ms.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-jdv-j407-type-repas-ms.xlsx
@@ -117,7 +117,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r427-type-repas</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r425-type-repas</t>
   </si>
 </sst>
 </file>
